--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/78.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/78.xlsx
@@ -426,13 +426,13 @@
         <v>-4.47570245665683</v>
       </c>
       <c r="E2">
-        <v>-7.40569347191379</v>
+        <v>-9.070175974565325</v>
       </c>
       <c r="F2">
-        <v>-2.24107111735311</v>
+        <v>-2.42669665517684</v>
       </c>
       <c r="G2">
-        <v>-10.25526267343842</v>
+        <v>-8.44504025331984</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.268319119402142</v>
       </c>
       <c r="E3">
-        <v>-8.192033431677553</v>
+        <v>-9.492158858013203</v>
       </c>
       <c r="F3">
-        <v>-1.653853891019582</v>
+        <v>-2.689251845331157</v>
       </c>
       <c r="G3">
-        <v>-9.915256267731673</v>
+        <v>-8.729164976426109</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.994735749133286</v>
       </c>
       <c r="E4">
-        <v>-8.640401666672068</v>
+        <v>-9.87230229057476</v>
       </c>
       <c r="F4">
-        <v>-1.827508691505457</v>
+        <v>-2.36933386926778</v>
       </c>
       <c r="G4">
-        <v>-9.651990088536104</v>
+        <v>-7.984720293876224</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.665241172170707</v>
       </c>
       <c r="E5">
-        <v>-10.74183522638616</v>
+        <v>-10.78195109457268</v>
       </c>
       <c r="F5">
-        <v>-1.52570876727611</v>
+        <v>-2.397857872415778</v>
       </c>
       <c r="G5">
-        <v>-9.839484627463792</v>
+        <v>-7.981383762288782</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.274727466040074</v>
       </c>
       <c r="E6">
-        <v>-10.84834848402272</v>
+        <v>-10.95037627342845</v>
       </c>
       <c r="F6">
-        <v>-1.347641253635523</v>
+        <v>-2.242232488451835</v>
       </c>
       <c r="G6">
-        <v>-8.857706291741867</v>
+        <v>-7.697306032585153</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.826042338988948</v>
       </c>
       <c r="E7">
-        <v>-11.89754518853488</v>
+        <v>-12.29955943193298</v>
       </c>
       <c r="F7">
-        <v>-1.481123548555232</v>
+        <v>-2.330403914805814</v>
       </c>
       <c r="G7">
-        <v>-8.90718381786035</v>
+        <v>-7.477671922368566</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.313480781519789</v>
       </c>
       <c r="E8">
-        <v>-10.70883380919908</v>
+        <v>-12.8270338830315</v>
       </c>
       <c r="F8">
-        <v>-1.765324807312103</v>
+        <v>-1.864479557059801</v>
       </c>
       <c r="G8">
-        <v>-8.763209085894225</v>
+        <v>-7.10877632238885</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-1.737970346845337</v>
       </c>
       <c r="E9">
-        <v>-12.8199734237793</v>
+        <v>-13.69413303700656</v>
       </c>
       <c r="F9">
-        <v>-1.459464226074233</v>
+        <v>-2.116072961372873</v>
       </c>
       <c r="G9">
-        <v>-7.988505873533338</v>
+        <v>-6.813887499333422</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.104617488060119</v>
       </c>
       <c r="E10">
-        <v>-12.51597496764715</v>
+        <v>-14.15954189806684</v>
       </c>
       <c r="F10">
-        <v>-1.403922191716527</v>
+        <v>-1.895009037689977</v>
       </c>
       <c r="G10">
-        <v>-8.144689752579804</v>
+        <v>-6.277849419886042</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.4325601764990576</v>
       </c>
       <c r="E11">
-        <v>-13.67333790790314</v>
+        <v>-14.98888420788788</v>
       </c>
       <c r="F11">
-        <v>-1.360731943701963</v>
+        <v>-1.808085961012017</v>
       </c>
       <c r="G11">
-        <v>-7.248338895995992</v>
+        <v>-6.094515102464294</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>0.2440386549313258</v>
       </c>
       <c r="E12">
-        <v>-14.90200318018379</v>
+        <v>-15.15762503080434</v>
       </c>
       <c r="F12">
-        <v>-0.9418754217830184</v>
+        <v>-1.677754775692556</v>
       </c>
       <c r="G12">
-        <v>-6.201764490267228</v>
+        <v>-5.543715873098759</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>0.8840693862255667</v>
       </c>
       <c r="E13">
-        <v>-15.40344945590962</v>
+        <v>-16.73143462381222</v>
       </c>
       <c r="F13">
-        <v>-1.25370770362767</v>
+        <v>-1.429261122200761</v>
       </c>
       <c r="G13">
-        <v>-6.620360835027967</v>
+        <v>-5.121420103252412</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>1.443303100831901</v>
       </c>
       <c r="E14">
-        <v>-15.90377021136641</v>
+        <v>-16.7378721013657</v>
       </c>
       <c r="F14">
-        <v>-0.5645366740923848</v>
+        <v>-1.213560049083589</v>
       </c>
       <c r="G14">
-        <v>-6.335794896085802</v>
+        <v>-4.756785238445393</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>1.88866126857552</v>
       </c>
       <c r="E15">
-        <v>-17.6851365403326</v>
+        <v>-18.27307344189797</v>
       </c>
       <c r="F15">
-        <v>-0.5864544472030569</v>
+        <v>-1.195647432365452</v>
       </c>
       <c r="G15">
-        <v>-6.06146568668539</v>
+        <v>-4.381125199230103</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>2.204066194684536</v>
       </c>
       <c r="E16">
-        <v>-17.31946289602674</v>
+        <v>-18.63531238043819</v>
       </c>
       <c r="F16">
-        <v>-0.08201431869647841</v>
+        <v>-0.6342147981788653</v>
       </c>
       <c r="G16">
-        <v>-5.707968258304061</v>
+        <v>-3.900941389565</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>2.392228166171332</v>
       </c>
       <c r="E17">
-        <v>-18.37751840029476</v>
+        <v>-19.83867628932799</v>
       </c>
       <c r="F17">
-        <v>-0.3285613087916953</v>
+        <v>-0.5743652533266009</v>
       </c>
       <c r="G17">
-        <v>-4.8592830710925</v>
+        <v>-4.184948629164668</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>2.473438227504065</v>
       </c>
       <c r="E18">
-        <v>-19.39907133022886</v>
+        <v>-20.1625229423815</v>
       </c>
       <c r="F18">
-        <v>-0.01723764453236266</v>
+        <v>-0.1691453155925416</v>
       </c>
       <c r="G18">
-        <v>-5.003390951032772</v>
+        <v>-3.551292198710971</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>2.478701395320387</v>
       </c>
       <c r="E19">
-        <v>-21.93364329900933</v>
+        <v>-21.55246571682789</v>
       </c>
       <c r="F19">
-        <v>1.381039904453981</v>
+        <v>0.293300727429116</v>
       </c>
       <c r="G19">
-        <v>-3.905627676106048</v>
+        <v>-3.097599614411895</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>2.443450416776478</v>
       </c>
       <c r="E20">
-        <v>-22.45890824168304</v>
+        <v>-22.17104501154785</v>
       </c>
       <c r="F20">
-        <v>0.8375000061678625</v>
+        <v>0.6297462899131492</v>
       </c>
       <c r="G20">
-        <v>-5.304187889097889</v>
+        <v>-2.640528726611919</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.400015395170022</v>
       </c>
       <c r="E21">
-        <v>-22.34255602641797</v>
+        <v>-23.39123773272586</v>
       </c>
       <c r="F21">
-        <v>1.024916474316445</v>
+        <v>0.9738476239338555</v>
       </c>
       <c r="G21">
-        <v>-4.058729571162705</v>
+        <v>-2.641593910405093</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.376594385621374</v>
       </c>
       <c r="E22">
-        <v>-23.03314785229914</v>
+        <v>-23.28337468140873</v>
       </c>
       <c r="F22">
-        <v>1.907033324413999</v>
+        <v>1.174917243615379</v>
       </c>
       <c r="G22">
-        <v>-4.129331937140181</v>
+        <v>-2.559775785664194</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.390172183922224</v>
       </c>
       <c r="E23">
-        <v>-24.38665450379281</v>
+        <v>-24.0157353535837</v>
       </c>
       <c r="F23">
-        <v>1.271374000732159</v>
+        <v>0.8392594585314086</v>
       </c>
       <c r="G23">
-        <v>-3.814160239356394</v>
+        <v>-2.537281610267162</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.453595520402714</v>
       </c>
       <c r="E24">
-        <v>-23.99105697189157</v>
+        <v>-23.99699606408607</v>
       </c>
       <c r="F24">
-        <v>1.783323279745116</v>
+        <v>1.219471812742354</v>
       </c>
       <c r="G24">
-        <v>-3.827135639974228</v>
+        <v>-2.142409101605869</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.571374740385227</v>
       </c>
       <c r="E25">
-        <v>-24.04779399180005</v>
+        <v>-24.39964159560555</v>
       </c>
       <c r="F25">
-        <v>1.75293876341043</v>
+        <v>1.166570613664772</v>
       </c>
       <c r="G25">
-        <v>-2.984113157780792</v>
+        <v>-2.25026157140935</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.740547608707654</v>
       </c>
       <c r="E26">
-        <v>-24.88378559295214</v>
+        <v>-24.39402230068305</v>
       </c>
       <c r="F26">
-        <v>1.885084901709424</v>
+        <v>1.553023887888408</v>
       </c>
       <c r="G26">
-        <v>-3.506938258852548</v>
+        <v>-2.210168366723623</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.958982618215161</v>
       </c>
       <c r="E27">
-        <v>-24.49215853107743</v>
+        <v>-24.55158267871307</v>
       </c>
       <c r="F27">
-        <v>1.756298621596184</v>
+        <v>1.353034459300135</v>
       </c>
       <c r="G27">
-        <v>-3.422692141641913</v>
+        <v>-2.140484982842218</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>3.213224753712751</v>
       </c>
       <c r="E28">
-        <v>-24.00029371387798</v>
+        <v>-24.66743650861917</v>
       </c>
       <c r="F28">
-        <v>1.969649616391614</v>
+        <v>1.259599586468767</v>
       </c>
       <c r="G28">
-        <v>-3.868871003007765</v>
+        <v>-2.223209035956234</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>3.492421362678705</v>
       </c>
       <c r="E29">
-        <v>-25.08171518505949</v>
+        <v>-24.42356409283656</v>
       </c>
       <c r="F29">
-        <v>2.434458163246056</v>
+        <v>1.165203807450153</v>
       </c>
       <c r="G29">
-        <v>-4.836149263270646</v>
+        <v>-2.339348009091908</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>3.781889868240681</v>
       </c>
       <c r="E30">
-        <v>-23.91364941921941</v>
+        <v>-23.9126277292335</v>
       </c>
       <c r="F30">
-        <v>1.854332590247895</v>
+        <v>1.089225949265382</v>
       </c>
       <c r="G30">
-        <v>-3.639913923856311</v>
+        <v>-2.261537377298368</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>4.064488619113739</v>
       </c>
       <c r="E31">
-        <v>-24.26612000472364</v>
+        <v>-23.67791314442215</v>
       </c>
       <c r="F31">
-        <v>1.432145203002293</v>
+        <v>1.044913263420025</v>
       </c>
       <c r="G31">
-        <v>-2.776783486822122</v>
+        <v>-2.351365266444803</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>4.331124315485409</v>
       </c>
       <c r="E32">
-        <v>-24.28096358199857</v>
+        <v>-24.1743631069242</v>
       </c>
       <c r="F32">
-        <v>1.692255880950949</v>
+        <v>1.063877906739717</v>
       </c>
       <c r="G32">
-        <v>-3.44144512003988</v>
+        <v>-2.181439733243012</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>4.567619136340868</v>
       </c>
       <c r="E33">
-        <v>-23.3101504348199</v>
+        <v>-23.15144377046423</v>
       </c>
       <c r="F33">
-        <v>1.464723236219592</v>
+        <v>1.209736839024654</v>
       </c>
       <c r="G33">
-        <v>-3.137003582525568</v>
+        <v>-2.057917574403669</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>4.767712270026346</v>
       </c>
       <c r="E34">
-        <v>-22.67259927076812</v>
+        <v>-22.88808864035685</v>
       </c>
       <c r="F34">
-        <v>1.035893999138344</v>
+        <v>1.142378972033415</v>
       </c>
       <c r="G34">
-        <v>-2.552857312497744</v>
+        <v>-2.432956256406275</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>4.926382495028683</v>
       </c>
       <c r="E35">
-        <v>-22.93591702197358</v>
+        <v>-22.73665424903095</v>
       </c>
       <c r="F35">
-        <v>1.26313340180911</v>
+        <v>0.927533602443335</v>
       </c>
       <c r="G35">
-        <v>-3.60712558253652</v>
+        <v>-2.619397359891448</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>5.037114267572592</v>
       </c>
       <c r="E36">
-        <v>-22.56426690657129</v>
+        <v>-22.35129022983408</v>
       </c>
       <c r="F36">
-        <v>1.373995468060573</v>
+        <v>0.9056481356613721</v>
       </c>
       <c r="G36">
-        <v>-3.89395242629459</v>
+        <v>-2.548531308710269</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>5.10330129959869</v>
       </c>
       <c r="E37">
-        <v>-20.93644480028402</v>
+        <v>-21.70727666896087</v>
       </c>
       <c r="F37">
-        <v>1.293559336513936</v>
+        <v>0.7916515271577154</v>
       </c>
       <c r="G37">
-        <v>-3.831466865250885</v>
+        <v>-2.505208612965335</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>5.12598503659836</v>
       </c>
       <c r="E38">
-        <v>-21.37656475758743</v>
+        <v>-21.15840902632816</v>
       </c>
       <c r="F38">
-        <v>1.255719513554054</v>
+        <v>1.010222893325587</v>
       </c>
       <c r="G38">
-        <v>-4.423912692333858</v>
+        <v>-2.415250186589345</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>5.116126880397045</v>
       </c>
       <c r="E39">
-        <v>-21.22126372651811</v>
+        <v>-20.77490149259349</v>
       </c>
       <c r="F39">
-        <v>1.07159000725978</v>
+        <v>0.7299066776878458</v>
       </c>
       <c r="G39">
-        <v>-3.390005619361175</v>
+        <v>-2.342828131631862</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>5.086275221673874</v>
       </c>
       <c r="E40">
-        <v>-19.85187934812962</v>
+        <v>-20.3410404247566</v>
       </c>
       <c r="F40">
-        <v>1.108121009723239</v>
+        <v>1.109956671887842</v>
       </c>
       <c r="G40">
-        <v>-3.462774903349275</v>
+        <v>-2.658177360047845</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>5.042953040366537</v>
       </c>
       <c r="E41">
-        <v>-20.13383255854958</v>
+        <v>-19.01304279722002</v>
       </c>
       <c r="F41">
-        <v>1.100176966330391</v>
+        <v>0.7846402254604203</v>
       </c>
       <c r="G41">
-        <v>-3.389201510027112</v>
+        <v>-3.05120146153863</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>4.998172707642495</v>
       </c>
       <c r="E42">
-        <v>-19.30535411668411</v>
+        <v>-19.07585181208541</v>
       </c>
       <c r="F42">
-        <v>1.673541404586903</v>
+        <v>0.579775026339269</v>
       </c>
       <c r="G42">
-        <v>-4.100211691970904</v>
+        <v>-2.526478349149135</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>4.952154824772744</v>
       </c>
       <c r="E43">
-        <v>-18.46280459485012</v>
+        <v>-18.01245527805366</v>
       </c>
       <c r="F43">
-        <v>1.519697010538978</v>
+        <v>0.6258579333244083</v>
       </c>
       <c r="G43">
-        <v>-3.642895394179363</v>
+        <v>-2.783023166394882</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>4.906174180262055</v>
       </c>
       <c r="E44">
-        <v>-16.76088089210525</v>
+        <v>-17.88385108938034</v>
       </c>
       <c r="F44">
-        <v>1.28765142019717</v>
+        <v>0.4931145421279959</v>
       </c>
       <c r="G44">
-        <v>-4.002559401284903</v>
+        <v>-2.579575672643197</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>4.859083609309231</v>
       </c>
       <c r="E45">
-        <v>-16.86540891472854</v>
+        <v>-17.21443233483315</v>
       </c>
       <c r="F45">
-        <v>1.293274378127373</v>
+        <v>0.7437486969886256</v>
       </c>
       <c r="G45">
-        <v>-3.496952160791539</v>
+        <v>-2.581426690558297</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>4.801488872148032</v>
       </c>
       <c r="E46">
-        <v>-17.0607801286598</v>
+        <v>-16.45042003915167</v>
       </c>
       <c r="F46">
-        <v>1.440750283582574</v>
+        <v>0.608283290506614</v>
       </c>
       <c r="G46">
-        <v>-3.865725055775473</v>
+        <v>-2.824544448371948</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>4.730905073689986</v>
       </c>
       <c r="E47">
-        <v>-17.53879813930226</v>
+        <v>-15.92564102220296</v>
       </c>
       <c r="F47">
-        <v>1.537989019527597</v>
+        <v>0.996337798919862</v>
       </c>
       <c r="G47">
-        <v>-3.727849023174189</v>
+        <v>-3.182051980445228</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>4.637099537300453</v>
       </c>
       <c r="E48">
-        <v>-14.39835154924448</v>
+        <v>-15.72011935979382</v>
       </c>
       <c r="F48">
-        <v>0.5766934996008549</v>
+        <v>0.3754184448034366</v>
       </c>
       <c r="G48">
-        <v>-4.771794409099703</v>
+        <v>-3.282184478492787</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>4.512838029617019</v>
       </c>
       <c r="E49">
-        <v>-15.5401441002437</v>
+        <v>-14.71955260668408</v>
       </c>
       <c r="F49">
-        <v>0.8857358400328776</v>
+        <v>0.715569294680192</v>
       </c>
       <c r="G49">
-        <v>-4.023223444723564</v>
+        <v>-2.963584873060868</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>4.352684786905153</v>
       </c>
       <c r="E50">
-        <v>-13.54820995710871</v>
+        <v>-14.34852962619184</v>
       </c>
       <c r="F50">
-        <v>1.131818944382527</v>
+        <v>0.6071550541040011</v>
       </c>
       <c r="G50">
-        <v>-4.732567971618226</v>
+        <v>-3.056216701898159</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>4.147479601873093</v>
       </c>
       <c r="E51">
-        <v>-13.23730055733204</v>
+        <v>-13.27411877572665</v>
       </c>
       <c r="F51">
-        <v>0.8342677165621387</v>
+        <v>0.5118041674699584</v>
       </c>
       <c r="G51">
-        <v>-3.978451785730563</v>
+        <v>-2.953925118073749</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>3.895291281910516</v>
       </c>
       <c r="E52">
-        <v>-12.87285211036701</v>
+        <v>-13.19447679536174</v>
       </c>
       <c r="F52">
-        <v>0.5513363450337592</v>
+        <v>0.7048402800791328</v>
       </c>
       <c r="G52">
-        <v>-4.159065707288371</v>
+        <v>-3.260319492542213</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>3.592925512901398</v>
       </c>
       <c r="E53">
-        <v>-13.28078052669167</v>
+        <v>-12.57007469836436</v>
       </c>
       <c r="F53">
-        <v>0.7045743741428342</v>
+        <v>0.5793078271240901</v>
       </c>
       <c r="G53">
-        <v>-4.193026272929572</v>
+        <v>-3.417465430970504</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>3.240867153370147</v>
       </c>
       <c r="E54">
-        <v>-13.77726786809565</v>
+        <v>-12.75155342041407</v>
       </c>
       <c r="F54">
-        <v>0.6711431225006517</v>
+        <v>0.5546141948466369</v>
       </c>
       <c r="G54">
-        <v>-4.281527903823721</v>
+        <v>-4.138007441416451</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>2.841202111517465</v>
       </c>
       <c r="E55">
-        <v>-13.07085230706689</v>
+        <v>-12.13419932303493</v>
       </c>
       <c r="F55">
-        <v>0.5151201221833648</v>
+        <v>0.6708225443157683</v>
       </c>
       <c r="G55">
-        <v>-5.160505560525969</v>
+        <v>-4.273800099834026</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>2.394516623483474</v>
       </c>
       <c r="E56">
-        <v>-13.86235470850741</v>
+        <v>-11.13062979813734</v>
       </c>
       <c r="F56">
-        <v>1.156002302339856</v>
+        <v>0.3882366019943562</v>
       </c>
       <c r="G56">
-        <v>-4.897637519880546</v>
+        <v>-3.975269288073995</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>1.904511710273969</v>
       </c>
       <c r="E57">
-        <v>-11.91141276114848</v>
+        <v>-12.0762661782649</v>
       </c>
       <c r="F57">
-        <v>0.7440005206790766</v>
+        <v>0.4934177245974206</v>
       </c>
       <c r="G57">
-        <v>-5.060960480011411</v>
+        <v>-4.741909215765229</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>1.374210395144601</v>
       </c>
       <c r="E58">
-        <v>-10.93143762978724</v>
+        <v>-11.06896291638628</v>
       </c>
       <c r="F58">
-        <v>0.602275970101512</v>
+        <v>0.7702249759169033</v>
       </c>
       <c r="G58">
-        <v>-5.649769539878964</v>
+        <v>-4.705836557749818</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.807328608173012</v>
       </c>
       <c r="E59">
-        <v>-11.07423749476882</v>
+        <v>-10.6653123077262</v>
       </c>
       <c r="F59">
-        <v>1.258799383557663</v>
+        <v>0.5122216646409693</v>
       </c>
       <c r="G59">
-        <v>-6.338698044071119</v>
+        <v>-4.845020573391249</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.2088638536039776</v>
       </c>
       <c r="E60">
-        <v>-10.09033757870561</v>
+        <v>-10.26098057240884</v>
       </c>
       <c r="F60">
-        <v>0.6184639258870199</v>
+        <v>0.4025938658196772</v>
       </c>
       <c r="G60">
-        <v>-5.696191189453549</v>
+        <v>-4.690892655710285</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.4145883183463392</v>
       </c>
       <c r="E61">
-        <v>-10.86021420877775</v>
+        <v>-10.01392264354009</v>
       </c>
       <c r="F61">
-        <v>0.698055122682802</v>
+        <v>0.4086757392910311</v>
       </c>
       <c r="G61">
-        <v>-6.18509749679756</v>
+        <v>-4.949335484273771</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.054717062734416</v>
       </c>
       <c r="E62">
-        <v>-9.909585668637746</v>
+        <v>-8.994683052313917</v>
       </c>
       <c r="F62">
-        <v>0.7207747554393841</v>
+        <v>0.6855906783728779</v>
       </c>
       <c r="G62">
-        <v>-5.465422253555864</v>
+        <v>-4.859215191733131</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.700691208998996</v>
       </c>
       <c r="E63">
-        <v>-8.455035538822321</v>
+        <v>-9.001033312429579</v>
       </c>
       <c r="F63">
-        <v>1.025791230293801</v>
+        <v>0.4496882094036347</v>
       </c>
       <c r="G63">
-        <v>-6.40736323756199</v>
+        <v>-5.589748521729269</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.340672230911221</v>
       </c>
       <c r="E64">
-        <v>-8.966922987818762</v>
+        <v>-9.802652936657386</v>
       </c>
       <c r="F64">
-        <v>0.8442329764178168</v>
+        <v>0.4416778966185634</v>
       </c>
       <c r="G64">
-        <v>-6.601124868880645</v>
+        <v>-5.516705109559101</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.962463085104612</v>
       </c>
       <c r="E65">
-        <v>-9.338340523386854</v>
+        <v>-8.631854357765571</v>
       </c>
       <c r="F65">
-        <v>0.8106277676210465</v>
+        <v>0.6543032415691405</v>
       </c>
       <c r="G65">
-        <v>-6.191861936033135</v>
+        <v>-6.017900191693483</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.551339199177655</v>
       </c>
       <c r="E66">
-        <v>-9.029528495329227</v>
+        <v>-8.819434147251451</v>
       </c>
       <c r="F66">
-        <v>0.7151783052660706</v>
+        <v>0.4933680225532526</v>
       </c>
       <c r="G66">
-        <v>-6.381169637079351</v>
+        <v>-5.87896941827739</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.095525146487799</v>
       </c>
       <c r="E67">
-        <v>-8.125278866053582</v>
+        <v>-8.19793099175881</v>
       </c>
       <c r="F67">
-        <v>0.3236338849848283</v>
+        <v>0.5033548199614034</v>
       </c>
       <c r="G67">
-        <v>-6.736027263392651</v>
+        <v>-5.997862726956689</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.582974171644884</v>
       </c>
       <c r="E68">
-        <v>-9.46757184697022</v>
+        <v>-8.498316154038358</v>
       </c>
       <c r="F68">
-        <v>0.5964533756272343</v>
+        <v>0.2130368963022607</v>
       </c>
       <c r="G68">
-        <v>-7.094652194150927</v>
+        <v>-6.017325827883439</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.004408886773354</v>
       </c>
       <c r="E69">
-        <v>-8.478953882842008</v>
+        <v>-8.122371618126204</v>
       </c>
       <c r="F69">
-        <v>0.4335830903584067</v>
+        <v>0.2826437807921003</v>
       </c>
       <c r="G69">
-        <v>-6.454709090721829</v>
+        <v>-5.737101557196294</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.356049511401131</v>
       </c>
       <c r="E70">
-        <v>-6.581210419342803</v>
+        <v>-8.162288132169131</v>
       </c>
       <c r="F70">
-        <v>0.7777299845862669</v>
+        <v>0.1132045420190727</v>
       </c>
       <c r="G70">
-        <v>-6.464496772193913</v>
+        <v>-6.123776327841492</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.633022310918565</v>
       </c>
       <c r="E71">
-        <v>-8.632809596370281</v>
+        <v>-8.217521689578025</v>
       </c>
       <c r="F71">
-        <v>0.8428131546894184</v>
+        <v>0.1567277937295615</v>
       </c>
       <c r="G71">
-        <v>-7.389261667535106</v>
+        <v>-5.944976873774507</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.837763169073161</v>
       </c>
       <c r="E72">
-        <v>-7.260036197540728</v>
+        <v>-7.519445776889519</v>
       </c>
       <c r="F72">
-        <v>0.552725517168254</v>
+        <v>0.342871889547444</v>
       </c>
       <c r="G72">
-        <v>-7.434464099385641</v>
+        <v>-5.897409107324423</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.972892801668212</v>
       </c>
       <c r="E73">
-        <v>-9.764580448442683</v>
+        <v>-8.163205991871918</v>
       </c>
       <c r="F73">
-        <v>0.6466690075849403</v>
+        <v>0.2433021277309435</v>
       </c>
       <c r="G73">
-        <v>-6.973179469815608</v>
+        <v>-5.750129172705949</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.041556188434601</v>
       </c>
       <c r="E74">
-        <v>-9.954157932575805</v>
+        <v>-8.478800214022989</v>
       </c>
       <c r="F74">
-        <v>0.3509733227468232</v>
+        <v>0.01329100773041032</v>
       </c>
       <c r="G74">
-        <v>-6.134926817990136</v>
+        <v>-5.870990982806948</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.050533641033993</v>
       </c>
       <c r="E75">
-        <v>-8.53328204018209</v>
+        <v>-8.515277869088958</v>
       </c>
       <c r="F75">
-        <v>0.2638414974833572</v>
+        <v>-0.253618909860424</v>
       </c>
       <c r="G75">
-        <v>-6.387751324193547</v>
+        <v>-5.708584394027564</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.999557341233627</v>
       </c>
       <c r="E76">
-        <v>-9.062650355644735</v>
+        <v>-9.25111062593148</v>
       </c>
       <c r="F76">
-        <v>0.4385524664078009</v>
+        <v>-0.04010721178885142</v>
       </c>
       <c r="G76">
-        <v>-6.282366008028668</v>
+        <v>-5.925041228076766</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.890925906227093</v>
       </c>
       <c r="E77">
-        <v>-10.13324440490241</v>
+        <v>-9.948526178019339</v>
       </c>
       <c r="F77">
-        <v>0.1560982345034339</v>
+        <v>-0.02523553180639189</v>
       </c>
       <c r="G77">
-        <v>-6.90325328668723</v>
+        <v>-5.6030476546764</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.723238157463503</v>
       </c>
       <c r="E78">
-        <v>-10.39824420669442</v>
+        <v>-10.23196623809359</v>
       </c>
       <c r="F78">
-        <v>0.1052472447477806</v>
+        <v>-0.1073582193851293</v>
       </c>
       <c r="G78">
-        <v>-5.807072122982722</v>
+        <v>-5.296689830632212</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.493341534123519</v>
       </c>
       <c r="E79">
-        <v>-10.13766342175203</v>
+        <v>-10.29975910654876</v>
       </c>
       <c r="F79">
-        <v>0.4150235186986838</v>
+        <v>0.05508545667125657</v>
       </c>
       <c r="G79">
-        <v>-6.437321531745015</v>
+        <v>-5.090832619622929</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.201636283797702</v>
       </c>
       <c r="E80">
-        <v>-11.72392849552307</v>
+        <v>-11.08516044055311</v>
       </c>
       <c r="F80">
-        <v>0.3811648294766568</v>
+        <v>-0.1573758715335662</v>
       </c>
       <c r="G80">
-        <v>-5.918879870841739</v>
+        <v>-4.937422656704522</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.843389459092786</v>
       </c>
       <c r="E81">
-        <v>-12.22907528253931</v>
+        <v>-11.50120423180649</v>
       </c>
       <c r="F81">
-        <v>0.05829703709191025</v>
+        <v>0.08579717813004824</v>
       </c>
       <c r="G81">
-        <v>-5.422997653950272</v>
+        <v>-4.413208639510294</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.417578976551381</v>
       </c>
       <c r="E82">
-        <v>-12.81301264159888</v>
+        <v>-11.86589356502836</v>
       </c>
       <c r="F82">
-        <v>0.6498366845332456</v>
+        <v>0.05443601662746176</v>
       </c>
       <c r="G82">
-        <v>-4.517654087622372</v>
+        <v>-4.328090533606227</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.923316771162611</v>
       </c>
       <c r="E83">
-        <v>-12.67342736218272</v>
+        <v>-13.40229518363351</v>
       </c>
       <c r="F83">
-        <v>0.4957528923059124</v>
+        <v>-0.1597889057779212</v>
       </c>
       <c r="G83">
-        <v>-5.869111246701346</v>
+        <v>-4.312987376146637</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.360742445182338</v>
       </c>
       <c r="E84">
-        <v>-14.52750396181268</v>
+        <v>-13.73268729773494</v>
       </c>
       <c r="F84">
-        <v>0.8188203212347336</v>
+        <v>0.04156815739237424</v>
       </c>
       <c r="G84">
-        <v>-5.507951282945099</v>
+        <v>-4.388926104068349</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.7353282814478</v>
       </c>
       <c r="E85">
-        <v>-14.46077016224533</v>
+        <v>-14.94027502254209</v>
       </c>
       <c r="F85">
-        <v>0.4091412817714045</v>
+        <v>0.1538434184330136</v>
       </c>
       <c r="G85">
-        <v>-5.826986882723733</v>
+        <v>-4.057672219603304</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.054465012572564</v>
       </c>
       <c r="E86">
-        <v>-17.19164366429382</v>
+        <v>-16.17019871785416</v>
       </c>
       <c r="F86">
-        <v>-0.282036053613461</v>
+        <v>0.03954859766434905</v>
       </c>
       <c r="G86">
-        <v>-5.200575268510376</v>
+        <v>-3.905956629924529</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.330991956336786</v>
       </c>
       <c r="E87">
-        <v>-16.89569413170919</v>
+        <v>-16.85457318638206</v>
       </c>
       <c r="F87">
-        <v>0.5939558479077938</v>
+        <v>0.1202879116804113</v>
       </c>
       <c r="G87">
-        <v>-5.174778501205585</v>
+        <v>-3.582331341154717</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.581712854737488</v>
       </c>
       <c r="E88">
-        <v>-18.85295311349319</v>
+        <v>-18.60876920686121</v>
       </c>
       <c r="F88">
-        <v>0.1514212721472279</v>
+        <v>0.02397694722652394</v>
       </c>
       <c r="G88">
-        <v>-4.06104008012584</v>
+        <v>-3.293473338104761</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.1749750866563979</v>
       </c>
       <c r="E89">
-        <v>-20.21473296194592</v>
+        <v>-19.69167752769701</v>
       </c>
       <c r="F89">
-        <v>0.2247814893391521</v>
+        <v>-0.002673288856341757</v>
       </c>
       <c r="G89">
-        <v>-4.279243502306498</v>
+        <v>-3.371824394028662</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.9193672005502456</v>
       </c>
       <c r="E90">
-        <v>-22.04619532591218</v>
+        <v>-22.20840314741469</v>
       </c>
       <c r="F90">
-        <v>0.3512359152135106</v>
+        <v>0.1030123094950276</v>
       </c>
       <c r="G90">
-        <v>-4.312423455314956</v>
+        <v>-2.829102808428032</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>1.632989827200031</v>
       </c>
       <c r="E91">
-        <v>-23.37097836788334</v>
+        <v>-23.17549086403498</v>
       </c>
       <c r="F91">
-        <v>0.9271674640512977</v>
+        <v>0.1211709513317955</v>
       </c>
       <c r="G91">
-        <v>-4.053053812421624</v>
+        <v>-2.965190480984403</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.298216506583423</v>
       </c>
       <c r="E92">
-        <v>-25.41383918828338</v>
+        <v>-25.37833753787875</v>
       </c>
       <c r="F92">
-        <v>0.2405767989757331</v>
+        <v>-0.02596366675345266</v>
       </c>
       <c r="G92">
-        <v>-4.298696160254883</v>
+        <v>-2.988851659213663</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.897740068356878</v>
       </c>
       <c r="E93">
-        <v>-27.39320571394944</v>
+        <v>-27.05343980188787</v>
       </c>
       <c r="F93">
-        <v>0.924360955290613</v>
+        <v>0.0920670910018377</v>
       </c>
       <c r="G93">
-        <v>-4.111696357427212</v>
+        <v>-2.964446418775936</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>3.415690497552594</v>
       </c>
       <c r="E94">
-        <v>-30.91453500818459</v>
+        <v>-29.22775391393005</v>
       </c>
       <c r="F94">
-        <v>0.5626137388554717</v>
+        <v>-0.2628137880314985</v>
       </c>
       <c r="G94">
-        <v>-4.059105518383825</v>
+        <v>-2.661346803981457</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>3.840435926387222</v>
       </c>
       <c r="E95">
-        <v>-32.85981405190212</v>
+        <v>-31.30509884796014</v>
       </c>
       <c r="F95">
-        <v>0.4118856629768792</v>
+        <v>-0.1050528729031383</v>
       </c>
       <c r="G95">
-        <v>-4.426875887444772</v>
+        <v>-2.662205738951933</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>4.156545162347374</v>
       </c>
       <c r="E96">
-        <v>-34.65102556831381</v>
+        <v>-33.58356927021205</v>
       </c>
       <c r="F96">
-        <v>0.4034296885291019</v>
+        <v>-0.3161291708104803</v>
       </c>
       <c r="G96">
-        <v>-4.041261079103566</v>
+        <v>-2.83245239373843</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>4.361352716049864</v>
       </c>
       <c r="E97">
-        <v>-36.22194037302828</v>
+        <v>-36.09088578967332</v>
       </c>
       <c r="F97">
-        <v>0.7611924577567776</v>
+        <v>-0.3202933737443534</v>
       </c>
       <c r="G97">
-        <v>-4.528629657883412</v>
+        <v>-2.414448687999873</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>4.439964117936615</v>
       </c>
       <c r="E98">
-        <v>-38.51796849615589</v>
+        <v>-37.9789065854611</v>
       </c>
       <c r="F98">
-        <v>0.3296055855916099</v>
+        <v>-0.4417187811163161</v>
       </c>
       <c r="G98">
-        <v>-3.844128976517784</v>
+        <v>-3.010494731873992</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>4.407880523038445</v>
       </c>
       <c r="E99">
-        <v>-40.92517808644917</v>
+        <v>-39.93113187511941</v>
       </c>
       <c r="F99">
-        <v>0.3109358410673147</v>
+        <v>-0.348336095431325</v>
       </c>
       <c r="G99">
-        <v>-3.677832378297641</v>
+        <v>-2.405180544701421</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>4.249839125681334</v>
       </c>
       <c r="E100">
-        <v>-44.643789071825</v>
+        <v>-43.20211597372221</v>
       </c>
       <c r="F100">
-        <v>0.1475677069894046</v>
+        <v>-0.5036665805998716</v>
       </c>
       <c r="G100">
-        <v>-4.478291891422157</v>
+        <v>-2.766826106951616</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>4.021890730570172</v>
       </c>
       <c r="E101">
-        <v>-47.14193218577257</v>
+        <v>-44.68792732517962</v>
       </c>
       <c r="F101">
-        <v>0.1762457864743235</v>
+        <v>-0.8660748342224469</v>
       </c>
       <c r="G101">
-        <v>-3.660426544108689</v>
+        <v>-3.091989124285593</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>3.674457426178572</v>
       </c>
       <c r="E102">
-        <v>-48.05445189709877</v>
+        <v>-46.91911551310401</v>
       </c>
       <c r="F102">
-        <v>0.399198387835602</v>
+        <v>-0.8416023760415411</v>
       </c>
       <c r="G102">
-        <v>-4.154274990963678</v>
+        <v>-2.836974203370239</v>
       </c>
     </row>
   </sheetData>
